--- a/test_data/WTA/WTA Tools Menu/WTA Tools Menu_Test_Cases.xlsx
+++ b/test_data/WTA/WTA Tools Menu/WTA Tools Menu_Test_Cases.xlsx
@@ -614,7 +614,7 @@
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>Clicking 'Projects' navigated to https://regplus.reganalytics.com/wta/Project.</t>
+          <t>Clicking 'Projects' navigated to https://regplus.kaz.com.bd/wta/Project.</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
@@ -673,7 +673,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>Confirmed: a direct deep link to /wta/Project redirects to https://regplus.reganalytics.com/wta/Information instead of loading the target page - a real application limitation, not an automation bug.</t>
+          <t>Confirmed: a direct deep link to /wta/Project redirects to https://regplus.kaz.com.bd/wta/Information instead of loading the target page - a real application limitation, not an automation bug.</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -733,7 +733,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>Clicking 'Questionnaire Creator' navigated to https://regplus.reganalytics.com/wta/QuestionnaireCreator.</t>
+          <t>Clicking 'Questionnaire Creator' navigated to https://regplus.kaz.com.bd/wta/QuestionnaireCreator.</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -792,7 +792,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>Confirmed: a direct deep link to /wta/QuestionnaireCreator redirects to https://regplus.reganalytics.com/wta/Information instead of loading the target page - a real application limitation, not an automation bug.</t>
+          <t>Confirmed: a direct deep link to /wta/QuestionnaireCreator redirects to https://regplus.kaz.com.bd/wta/Information instead of loading the target page - a real application limitation, not an automation bug.</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">

--- a/test_data/WTA/WTA Tools Menu/WTA Tools Menu_Test_Cases.xlsx
+++ b/test_data/WTA/WTA Tools Menu/WTA Tools Menu_Test_Cases.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K6"/>
+  <dimension ref="A1:K5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -512,7 +512,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>ToolsMenu_01</t>
+          <t>ToolsMenu_02_Projects</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -522,12 +522,12 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>The Tools dropdown lists exactly its 2 known items</t>
+          <t>Tools &gt; Projects navigates to its page</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Opening the 'Tools' nav dropdown must show Projects and Questionnaire Creator - no more, no less.</t>
+          <t>Clicking 'Projects' in the Tools dropdown must navigate to /wta/Project.</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -537,69 +537,10 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Menu item: Projects</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
-        <is>
-          <t>1. Log in
-2. Open the 'Tools' dropdown
-3. Verify each of the 2 items is visible</t>
-        </is>
-      </c>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>Opening the 'Tools' nav dropdown must show Projects and Questionnaire Creator - no more, no less.</t>
-        </is>
-      </c>
-      <c r="I2" s="2" t="inlineStr">
-        <is>
-          <t>The Tools dropdown showed both expected items: Projects, Questionnaire Creator.</t>
-        </is>
-      </c>
-      <c r="J2" s="2" t="inlineStr">
-        <is>
-          <t>[PASS] Both Tools dropdown items are visible</t>
-        </is>
-      </c>
-      <c r="K2" s="3" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>ToolsMenu_02_Projects</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>WTA Tools Menu</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>Tools &gt; Projects navigates to its page</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>Clicking 'Projects' in the Tools dropdown must navigate to /wta/Project.</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in.</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>Menu item: Projects</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
         <is>
           <t>1. Log in
 2. Open the Tools dropdown
@@ -607,19 +548,78 @@
 4. Verify the URL contains /wta/Project</t>
         </is>
       </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>Clicking 'Projects' in the Tools dropdown must navigate to /wta/Project.</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>Clicking 'Projects' navigated to https://regplusrc.reganalytics.com/wta/Project.</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>[PASS] URL contains /wta/Project</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>ToolsMenu_03_Projects</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>WTA Tools Menu</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>A direct deep link to /wta/Project redirects to /wta/Information (documented app behavior)</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>Unlike every Treaties page, a full-page `goto()` straight to /wta/Project does not land on that page - the SPA has no server-side route for a hard deep link to it, so it redirects to /wta/Information. This is a real, live-confirmed application behavior, documented here rather than hidden.</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in.</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>Direct URL: /wta/Project</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>1. Log in
+2. Navigate directly (full page load) to /wta/Project
+3. Verify the app redirects to /wta/Information rather than showing the target page</t>
+        </is>
+      </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>Clicking 'Projects' in the Tools dropdown must navigate to /wta/Project.</t>
+          <t>Unlike every Treaties page, a full-page `goto()` straight to /wta/Project does not land on that page - the SPA has no server-side route for a hard deep link to it, so it redirects to /wta/Information. This is a real, live-confirmed application behavior, documented here rather than hidden.</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>Clicking 'Projects' navigated to https://regplus.kaz.com.bd/wta/Project.</t>
+          <t>Confirmed: a direct deep link to /wta/Project redirects to https://regplusrc.reganalytics.com/wta/Information instead of loading the target page - a real application limitation, not an automation bug.</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>[PASS] URL contains /wta/Project</t>
+          <t>[PASS] Direct deep link redirected to /wta/Information</t>
         </is>
       </c>
       <c r="K3" s="3" t="inlineStr">
@@ -631,7 +631,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>ToolsMenu_03_Projects</t>
+          <t>ToolsMenu_02_QuestionnaireCreator</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -641,12 +641,12 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>A direct deep link to /wta/Project redirects to /wta/Information (documented app behavior)</t>
+          <t>Tools &gt; Questionnaire Creator navigates to its page</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Unlike every Treaties page, a full-page `goto()` straight to /wta/Project does not land on that page - the SPA has no server-side route for a hard deep link to it, so it redirects to /wta/Information. This is a real, live-confirmed application behavior, documented here rather than hidden.</t>
+          <t>Clicking 'Questionnaire Creator' in the Tools dropdown must navigate to /wta/QuestionnaireCreator.</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -656,69 +656,10 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>Direct URL: /wta/Project</t>
+          <t>Menu item: Questionnaire Creator</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>1. Log in
-2. Navigate directly (full page load) to /wta/Project
-3. Verify the app redirects to /wta/Information rather than showing the target page</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>Unlike every Treaties page, a full-page `goto()` straight to /wta/Project does not land on that page - the SPA has no server-side route for a hard deep link to it, so it redirects to /wta/Information. This is a real, live-confirmed application behavior, documented here rather than hidden.</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>Confirmed: a direct deep link to /wta/Project redirects to https://regplus.kaz.com.bd/wta/Information instead of loading the target page - a real application limitation, not an automation bug.</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>[PASS] Direct deep link redirected to /wta/Information</t>
-        </is>
-      </c>
-      <c r="K4" s="3" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>ToolsMenu_02_QuestionnaireCreator</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>WTA Tools Menu</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>Tools &gt; Questionnaire Creator navigates to its page</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>Clicking 'Questionnaire Creator' in the Tools dropdown must navigate to /wta/QuestionnaireCreator.</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in.</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>Menu item: Questionnaire Creator</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>1. Log in
 2. Open the Tools dropdown
@@ -726,81 +667,81 @@
 4. Verify the URL contains /wta/QuestionnaireCreator</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>Clicking 'Questionnaire Creator' in the Tools dropdown must navigate to /wta/QuestionnaireCreator.</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>Clicking 'Questionnaire Creator' navigated to https://regplus.kaz.com.bd/wta/QuestionnaireCreator.</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>Clicking 'Questionnaire Creator' navigated to https://regplusrc.reganalytics.com/wta/QuestionnaireCreator.</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>[PASS] URL contains /wta/QuestionnaireCreator</t>
         </is>
       </c>
-      <c r="K5" s="3" t="inlineStr">
+      <c r="K4" s="3" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>ToolsMenu_03_QuestionnaireCreator</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>WTA Tools Menu</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
+      <c r="C5" s="2" t="inlineStr">
         <is>
           <t>A direct deep link to /wta/QuestionnaireCreator redirects to /wta/Information (documented app behavior)</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="D5" s="2" t="inlineStr">
         <is>
           <t>Unlike every Treaties page, a full-page `goto()` straight to /wta/QuestionnaireCreator does not land on that page - the SPA has no server-side route for a hard deep link to it, so it redirects to /wta/Information. This is a real, live-confirmed application behavior, documented here rather than hidden.</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="E5" s="2" t="inlineStr">
         <is>
           <t>User is logged in.</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="F5" s="2" t="inlineStr">
         <is>
           <t>Direct URL: /wta/QuestionnaireCreator</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>1. Log in
 2. Navigate directly (full page load) to /wta/QuestionnaireCreator
 3. Verify the app redirects to /wta/Information rather than showing the target page</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>Unlike every Treaties page, a full-page `goto()` straight to /wta/QuestionnaireCreator does not land on that page - the SPA has no server-side route for a hard deep link to it, so it redirects to /wta/Information. This is a real, live-confirmed application behavior, documented here rather than hidden.</t>
         </is>
       </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>Confirmed: a direct deep link to /wta/QuestionnaireCreator redirects to https://regplus.kaz.com.bd/wta/Information instead of loading the target page - a real application limitation, not an automation bug.</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>Confirmed: a direct deep link to /wta/QuestionnaireCreator redirects to https://regplusrc.reganalytics.com/wta/Information instead of loading the target page - a real application limitation, not an automation bug.</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
         <is>
           <t>[PASS] Direct deep link redirected to /wta/Information</t>
         </is>
       </c>
-      <c r="K6" s="3" t="inlineStr">
+      <c r="K5" s="3" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>

--- a/test_data/WTA/WTA Tools Menu/WTA Tools Menu_Test_Cases.xlsx
+++ b/test_data/WTA/WTA Tools Menu/WTA Tools Menu_Test_Cases.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K5"/>
+  <dimension ref="A1:K2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -512,7 +512,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>ToolsMenu_02_Projects</t>
+          <t>ToolsMenu_01</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -522,12 +522,12 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Tools &gt; Projects navigates to its page</t>
+          <t>The Tools dropdown lists exactly its 2 known items</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Clicking 'Projects' in the Tools dropdown must navigate to /wta/Project.</t>
+          <t>Opening the 'Tools' nav dropdown must show Projects and Questionnaire Creator - no more, no less.</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -537,211 +537,32 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Menu item: Projects</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
           <t>1. Log in
-2. Open the Tools dropdown
-3. Click 'Projects'
-4. Verify the URL contains /wta/Project</t>
+2. Open the 'Tools' dropdown
+3. Verify each of the 2 items is visible</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>Clicking 'Projects' in the Tools dropdown must navigate to /wta/Project.</t>
+          <t>Opening the 'Tools' nav dropdown must show Projects and Questionnaire Creator - no more, no less.</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>Clicking 'Projects' navigated to https://regplusrc.reganalytics.com/wta/Project.</t>
+          <t>The Tools dropdown showed both expected items: Projects, Questionnaire Creator.</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>[PASS] URL contains /wta/Project</t>
+          <t>[PASS] Both Tools dropdown items are visible</t>
         </is>
       </c>
       <c r="K2" s="3" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>ToolsMenu_03_Projects</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>WTA Tools Menu</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>A direct deep link to /wta/Project redirects to /wta/Information (documented app behavior)</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>Unlike every Treaties page, a full-page `goto()` straight to /wta/Project does not land on that page - the SPA has no server-side route for a hard deep link to it, so it redirects to /wta/Information. This is a real, live-confirmed application behavior, documented here rather than hidden.</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in.</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>Direct URL: /wta/Project</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>1. Log in
-2. Navigate directly (full page load) to /wta/Project
-3. Verify the app redirects to /wta/Information rather than showing the target page</t>
-        </is>
-      </c>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>Unlike every Treaties page, a full-page `goto()` straight to /wta/Project does not land on that page - the SPA has no server-side route for a hard deep link to it, so it redirects to /wta/Information. This is a real, live-confirmed application behavior, documented here rather than hidden.</t>
-        </is>
-      </c>
-      <c r="I3" s="2" t="inlineStr">
-        <is>
-          <t>Confirmed: a direct deep link to /wta/Project redirects to https://regplusrc.reganalytics.com/wta/Information instead of loading the target page - a real application limitation, not an automation bug.</t>
-        </is>
-      </c>
-      <c r="J3" s="2" t="inlineStr">
-        <is>
-          <t>[PASS] Direct deep link redirected to /wta/Information</t>
-        </is>
-      </c>
-      <c r="K3" s="3" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>ToolsMenu_02_QuestionnaireCreator</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>WTA Tools Menu</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>Tools &gt; Questionnaire Creator navigates to its page</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>Clicking 'Questionnaire Creator' in the Tools dropdown must navigate to /wta/QuestionnaireCreator.</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in.</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>Menu item: Questionnaire Creator</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>1. Log in
-2. Open the Tools dropdown
-3. Click 'Questionnaire Creator'
-4. Verify the URL contains /wta/QuestionnaireCreator</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>Clicking 'Questionnaire Creator' in the Tools dropdown must navigate to /wta/QuestionnaireCreator.</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>Clicking 'Questionnaire Creator' navigated to https://regplusrc.reganalytics.com/wta/QuestionnaireCreator.</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>[PASS] URL contains /wta/QuestionnaireCreator</t>
-        </is>
-      </c>
-      <c r="K4" s="3" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>ToolsMenu_03_QuestionnaireCreator</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>WTA Tools Menu</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>A direct deep link to /wta/QuestionnaireCreator redirects to /wta/Information (documented app behavior)</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>Unlike every Treaties page, a full-page `goto()` straight to /wta/QuestionnaireCreator does not land on that page - the SPA has no server-side route for a hard deep link to it, so it redirects to /wta/Information. This is a real, live-confirmed application behavior, documented here rather than hidden.</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in.</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>Direct URL: /wta/QuestionnaireCreator</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>1. Log in
-2. Navigate directly (full page load) to /wta/QuestionnaireCreator
-3. Verify the app redirects to /wta/Information rather than showing the target page</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>Unlike every Treaties page, a full-page `goto()` straight to /wta/QuestionnaireCreator does not land on that page - the SPA has no server-side route for a hard deep link to it, so it redirects to /wta/Information. This is a real, live-confirmed application behavior, documented here rather than hidden.</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>Confirmed: a direct deep link to /wta/QuestionnaireCreator redirects to https://regplusrc.reganalytics.com/wta/Information instead of loading the target page - a real application limitation, not an automation bug.</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>[PASS] Direct deep link redirected to /wta/Information</t>
-        </is>
-      </c>
-      <c r="K5" s="3" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
